--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/96.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/96.xlsx
@@ -426,13 +426,13 @@
         <v>-12.91931961939501</v>
       </c>
       <c r="E2">
-        <v>-9.238229435049369</v>
+        <v>-11.69716365037033</v>
       </c>
       <c r="F2">
-        <v>-3.528075729856201</v>
+        <v>-3.9537836785637</v>
       </c>
       <c r="G2">
-        <v>-10.5771875275487</v>
+        <v>-10.65835548308055</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.37444392750462</v>
       </c>
       <c r="E3">
-        <v>-9.884886466396681</v>
+        <v>-12.62685483567104</v>
       </c>
       <c r="F3">
-        <v>-3.362196814180406</v>
+        <v>-4.016013951331611</v>
       </c>
       <c r="G3">
-        <v>-9.349928569594399</v>
+        <v>-9.67760636707146</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.73791270656147</v>
       </c>
       <c r="E4">
-        <v>-9.582837250085067</v>
+        <v>-12.72513630705951</v>
       </c>
       <c r="F4">
-        <v>-3.45283760376213</v>
+        <v>-4.050910584909345</v>
       </c>
       <c r="G4">
-        <v>-9.959337103008977</v>
+        <v>-9.926820924722255</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.07490542770156</v>
       </c>
       <c r="E5">
-        <v>-11.08500453401345</v>
+        <v>-13.35385152438844</v>
       </c>
       <c r="F5">
-        <v>-3.641458518114383</v>
+        <v>-4.190184824709429</v>
       </c>
       <c r="G5">
-        <v>-9.014639827922551</v>
+        <v>-9.873193397531601</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.37483545323423</v>
       </c>
       <c r="E6">
-        <v>-10.79559881713125</v>
+        <v>-13.9349453090527</v>
       </c>
       <c r="F6">
-        <v>-3.764679826015615</v>
+        <v>-4.539478365610883</v>
       </c>
       <c r="G6">
-        <v>-8.595398961920326</v>
+        <v>-9.700359746562871</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.649556670688686</v>
       </c>
       <c r="E7">
-        <v>-12.55764616741182</v>
+        <v>-14.46013055361826</v>
       </c>
       <c r="F7">
-        <v>-3.89082527084873</v>
+        <v>-4.432027516324148</v>
       </c>
       <c r="G7">
-        <v>-8.685429247860807</v>
+        <v>-9.235886896857584</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.895505423874544</v>
       </c>
       <c r="E8">
-        <v>-13.31641915824103</v>
+        <v>-15.53578804160821</v>
       </c>
       <c r="F8">
-        <v>-3.922256015213151</v>
+        <v>-4.441841184945114</v>
       </c>
       <c r="G8">
-        <v>-7.57080498078913</v>
+        <v>-8.903246591617155</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.113232885062558</v>
       </c>
       <c r="E9">
-        <v>-14.3871270241406</v>
+        <v>-15.95472622900581</v>
       </c>
       <c r="F9">
-        <v>-3.781161852229117</v>
+        <v>-4.030070517789715</v>
       </c>
       <c r="G9">
-        <v>-8.344989297329853</v>
+        <v>-8.577147924362324</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.306657910161128</v>
       </c>
       <c r="E10">
-        <v>-14.92798984572072</v>
+        <v>-16.14630332190031</v>
       </c>
       <c r="F10">
-        <v>-4.186923542244608</v>
+        <v>-4.365984268401151</v>
       </c>
       <c r="G10">
-        <v>-7.843335710673013</v>
+        <v>-8.707560244790834</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.480274483782098</v>
       </c>
       <c r="E11">
-        <v>-15.42353169943207</v>
+        <v>-17.47359905354849</v>
       </c>
       <c r="F11">
-        <v>-4.307030188711313</v>
+        <v>-4.530919673605158</v>
       </c>
       <c r="G11">
-        <v>-6.814146692333307</v>
+        <v>-8.119180296641705</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.657010655615231</v>
       </c>
       <c r="E12">
-        <v>-16.3529964610324</v>
+        <v>-18.56216722093431</v>
       </c>
       <c r="F12">
-        <v>-3.871892105490344</v>
+        <v>-4.552534264246406</v>
       </c>
       <c r="G12">
-        <v>-7.043908484395345</v>
+        <v>-7.061709287760007</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.858177547057394</v>
       </c>
       <c r="E13">
-        <v>-18.47875725818703</v>
+        <v>-19.03803738355634</v>
       </c>
       <c r="F13">
-        <v>-3.406453171042372</v>
+        <v>-4.263482914346143</v>
       </c>
       <c r="G13">
-        <v>-6.161379943990893</v>
+        <v>-7.234013251442454</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.127723555701501</v>
       </c>
       <c r="E14">
-        <v>-18.11644763825535</v>
+        <v>-19.97702552599481</v>
       </c>
       <c r="F14">
-        <v>-3.366918508376363</v>
+        <v>-3.887402456740362</v>
       </c>
       <c r="G14">
-        <v>-5.670826616527228</v>
+        <v>-6.038174681201377</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.501855934464794</v>
       </c>
       <c r="E15">
-        <v>-18.72285106414848</v>
+        <v>-21.27428841802412</v>
       </c>
       <c r="F15">
-        <v>-3.355618748634775</v>
+        <v>-3.729480009968456</v>
       </c>
       <c r="G15">
-        <v>-5.229855329605227</v>
+        <v>-6.121007841139481</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.027887405663313</v>
       </c>
       <c r="E16">
-        <v>-19.56808620920614</v>
+        <v>-21.06196638570049</v>
       </c>
       <c r="F16">
-        <v>-3.209196526515934</v>
+        <v>-3.580273645008806</v>
       </c>
       <c r="G16">
-        <v>-5.770073461249039</v>
+        <v>-5.279828014520525</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.737147232016488</v>
       </c>
       <c r="E17">
-        <v>-20.97983345262337</v>
+        <v>-21.87230963852905</v>
       </c>
       <c r="F17">
-        <v>-2.9096787544813</v>
+        <v>-3.549515534975458</v>
       </c>
       <c r="G17">
-        <v>-4.368812229750645</v>
+        <v>-5.441948740124175</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.656729899016965</v>
       </c>
       <c r="E18">
-        <v>-21.29737910698923</v>
+        <v>-23.77417815227045</v>
       </c>
       <c r="F18">
-        <v>-2.500368338512217</v>
+        <v>-3.244750055444089</v>
       </c>
       <c r="G18">
-        <v>-4.497224980673435</v>
+        <v>-5.491169931202059</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.789921922523905</v>
       </c>
       <c r="E19">
-        <v>-22.27204256766012</v>
+        <v>-23.66763221581798</v>
       </c>
       <c r="F19">
-        <v>-2.024060395372112</v>
+        <v>-2.801642249440786</v>
       </c>
       <c r="G19">
-        <v>-4.740791747634234</v>
+        <v>-5.438409766942694</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.129400614957283</v>
       </c>
       <c r="E20">
-        <v>-22.39425702417913</v>
+        <v>-24.47617313599149</v>
       </c>
       <c r="F20">
-        <v>-1.859081086695757</v>
+        <v>-2.468378446150906</v>
       </c>
       <c r="G20">
-        <v>-4.975463078731011</v>
+        <v>-5.452559038577539</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.645759833574339</v>
       </c>
       <c r="E21">
-        <v>-24.59083409786571</v>
+        <v>-25.15058518453182</v>
       </c>
       <c r="F21">
-        <v>-1.621164856570308</v>
+        <v>-2.314224242694334</v>
       </c>
       <c r="G21">
-        <v>-5.339331760043386</v>
+        <v>-5.021598841366295</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.30348307944035</v>
       </c>
       <c r="E22">
-        <v>-24.59161299539502</v>
+        <v>-26.0570543551212</v>
       </c>
       <c r="F22">
-        <v>-0.9943533251177699</v>
+        <v>-1.87526158717464</v>
       </c>
       <c r="G22">
-        <v>-5.373857439472445</v>
+        <v>-5.720570873800317</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.051365929448291</v>
       </c>
       <c r="E23">
-        <v>-25.63116496012183</v>
+        <v>-26.48514911696231</v>
       </c>
       <c r="F23">
-        <v>-0.7453709348583225</v>
+        <v>-1.638799141841104</v>
       </c>
       <c r="G23">
-        <v>-5.742218531081611</v>
+        <v>-5.773953420621065</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.83780603389686</v>
       </c>
       <c r="E24">
-        <v>-25.4104063807219</v>
+        <v>-26.61046557817657</v>
       </c>
       <c r="F24">
-        <v>-0.5012552030903222</v>
+        <v>-1.700772620714146</v>
       </c>
       <c r="G24">
-        <v>-6.45582979589029</v>
+        <v>-6.167703085970901</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.602458870826331</v>
       </c>
       <c r="E25">
-        <v>-26.14275119724235</v>
+        <v>-26.9285818202674</v>
       </c>
       <c r="F25">
-        <v>-0.2680225622603018</v>
+        <v>-1.055809902731465</v>
       </c>
       <c r="G25">
-        <v>-7.449956826423574</v>
+        <v>-6.199762408973204</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.291691733494747</v>
       </c>
       <c r="E26">
-        <v>-26.00561994734208</v>
+        <v>-28.07973349843923</v>
       </c>
       <c r="F26">
-        <v>-0.3411616053556785</v>
+        <v>-1.301188066421332</v>
       </c>
       <c r="G26">
-        <v>-7.663771720622943</v>
+        <v>-6.49366933140416</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.852742722056782</v>
       </c>
       <c r="E27">
-        <v>-26.21681891811181</v>
+        <v>-27.20185258426027</v>
       </c>
       <c r="F27">
-        <v>-0.1318348194030491</v>
+        <v>-1.182230365542309</v>
       </c>
       <c r="G27">
-        <v>-7.818314607487201</v>
+        <v>-7.106537384907278</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.247059732574316</v>
       </c>
       <c r="E28">
-        <v>-26.53125803930841</v>
+        <v>-27.01094570551891</v>
       </c>
       <c r="F28">
-        <v>0.1546808978772439</v>
+        <v>-1.063724953265214</v>
       </c>
       <c r="G28">
-        <v>-7.815527128143135</v>
+        <v>-7.447619581272849</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.44457698918151</v>
       </c>
       <c r="E29">
-        <v>-26.23563472761368</v>
+        <v>-27.18562706189078</v>
       </c>
       <c r="F29">
-        <v>0.125019546285202</v>
+        <v>-0.8425268340630653</v>
       </c>
       <c r="G29">
-        <v>-8.140735258647901</v>
+        <v>-7.870770201556953</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.430439663993994</v>
       </c>
       <c r="E30">
-        <v>-25.79619160990935</v>
+        <v>-27.47986013206516</v>
       </c>
       <c r="F30">
-        <v>-0.2156796828122066</v>
+        <v>-1.397235610041129</v>
       </c>
       <c r="G30">
-        <v>-8.80483731491678</v>
+        <v>-7.467711282150685</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.204005754101125</v>
       </c>
       <c r="E31">
-        <v>-25.25500273820068</v>
+        <v>-26.68077013714565</v>
       </c>
       <c r="F31">
-        <v>-0.08325189959626086</v>
+        <v>-1.097065912860492</v>
       </c>
       <c r="G31">
-        <v>-8.182554069899973</v>
+        <v>-7.572880692842253</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.779377001000099</v>
       </c>
       <c r="E32">
-        <v>-24.76392595986089</v>
+        <v>-26.6717086606563</v>
       </c>
       <c r="F32">
-        <v>-0.2770434832767884</v>
+        <v>-1.230167158774914</v>
       </c>
       <c r="G32">
-        <v>-7.983941200816938</v>
+        <v>-7.638161340331141</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.187264378742396</v>
       </c>
       <c r="E33">
-        <v>-24.72586413582642</v>
+        <v>-26.09311006517027</v>
       </c>
       <c r="F33">
-        <v>-0.3529459600279043</v>
+        <v>-1.311758034481054</v>
       </c>
       <c r="G33">
-        <v>-8.075769112985242</v>
+        <v>-7.497532676368441</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.462401182935509</v>
       </c>
       <c r="E34">
-        <v>-24.72206927460799</v>
+        <v>-26.48125010084171</v>
       </c>
       <c r="F34">
-        <v>-0.2584698293712179</v>
+        <v>-1.356433545248837</v>
       </c>
       <c r="G34">
-        <v>-7.957102608130067</v>
+        <v>-6.895106083496184</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.652167677363098</v>
       </c>
       <c r="E35">
-        <v>-24.15257744035138</v>
+        <v>-25.59933431632191</v>
       </c>
       <c r="F35">
-        <v>-0.09049514416633975</v>
+        <v>-1.473085899645869</v>
       </c>
       <c r="G35">
-        <v>-7.826928646980384</v>
+        <v>-5.947045294141859</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.799251013595962</v>
       </c>
       <c r="E36">
-        <v>-23.6960438617421</v>
+        <v>-25.26016067009542</v>
       </c>
       <c r="F36">
-        <v>-0.6388412301235005</v>
+        <v>-1.635151840166578</v>
       </c>
       <c r="G36">
-        <v>-7.321160052218229</v>
+        <v>-6.312751328228529</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.955265181283243</v>
       </c>
       <c r="E37">
-        <v>-23.79637220338204</v>
+        <v>-25.27773567771919</v>
       </c>
       <c r="F37">
-        <v>-0.7241812966947111</v>
+        <v>-1.839829828254697</v>
       </c>
       <c r="G37">
-        <v>-6.570775247559325</v>
+        <v>-6.345615113796874</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.158051553790482</v>
       </c>
       <c r="E38">
-        <v>-23.12321001366784</v>
+        <v>-24.99759069018267</v>
       </c>
       <c r="F38">
-        <v>-1.13061727777608</v>
+        <v>-1.931631160567743</v>
       </c>
       <c r="G38">
-        <v>-6.622323752151317</v>
+        <v>-6.047801747629578</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.447650405211344</v>
       </c>
       <c r="E39">
-        <v>-23.68549704577824</v>
+        <v>-23.99693831718176</v>
       </c>
       <c r="F39">
-        <v>-1.37390132867167</v>
+        <v>-1.863579121692958</v>
       </c>
       <c r="G39">
-        <v>-6.280966780505986</v>
+        <v>-5.550091020710008</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.847063455017826</v>
       </c>
       <c r="E40">
-        <v>-22.72825462461486</v>
+        <v>-24.05541450204281</v>
       </c>
       <c r="F40">
-        <v>-1.540656657059627</v>
+        <v>-2.212913252597149</v>
       </c>
       <c r="G40">
-        <v>-5.667986168454533</v>
+        <v>-5.065473501398256</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.378449090477414</v>
       </c>
       <c r="E41">
-        <v>-22.50370118399651</v>
+        <v>-23.58138289986789</v>
       </c>
       <c r="F41">
-        <v>-1.618693836607757</v>
+        <v>-2.204218708337365</v>
       </c>
       <c r="G41">
-        <v>-5.306256099560528</v>
+        <v>-4.610041751560718</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.047208109367107</v>
       </c>
       <c r="E42">
-        <v>-21.44808219349049</v>
+        <v>-22.96079176490873</v>
       </c>
       <c r="F42">
-        <v>-1.588009451273258</v>
+        <v>-2.617125067202001</v>
       </c>
       <c r="G42">
-        <v>-5.117058421991179</v>
+        <v>-6.242845848621278</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.8552363622962182</v>
       </c>
       <c r="E43">
-        <v>-21.27744023593346</v>
+        <v>-22.36363548293926</v>
       </c>
       <c r="F43">
-        <v>-1.617776005525456</v>
+        <v>-2.392786607175839</v>
       </c>
       <c r="G43">
-        <v>-5.8203970639915</v>
+        <v>-4.914750984086317</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.7906151487673603</v>
       </c>
       <c r="E44">
-        <v>-21.3571096791504</v>
+        <v>-22.71415748502898</v>
       </c>
       <c r="F44">
-        <v>-2.1972753327671</v>
+        <v>-2.37920221013733</v>
       </c>
       <c r="G44">
-        <v>-4.765256679169448</v>
+        <v>-5.385143089215821</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.837351915240053</v>
       </c>
       <c r="E45">
-        <v>-20.036765155104</v>
+        <v>-21.83051635191226</v>
       </c>
       <c r="F45">
-        <v>-2.310663091229699</v>
+        <v>-2.567684787133316</v>
       </c>
       <c r="G45">
-        <v>-4.904091027449864</v>
+        <v>-4.786543486986962</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.9714796825825444</v>
       </c>
       <c r="E46">
-        <v>-19.45952057334626</v>
+        <v>-21.36129398913349</v>
       </c>
       <c r="F46">
-        <v>-2.251672563374138</v>
+        <v>-2.613916800250959</v>
       </c>
       <c r="G46">
-        <v>-4.823793745394841</v>
+        <v>-5.468876717540607</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.167813733758218</v>
       </c>
       <c r="E47">
-        <v>-18.96300509772325</v>
+        <v>-21.54569345072583</v>
       </c>
       <c r="F47">
-        <v>-2.410508699391332</v>
+        <v>-2.853188239447388</v>
       </c>
       <c r="G47">
-        <v>-4.489802737574389</v>
+        <v>-4.740420966533835</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.399156793927934</v>
       </c>
       <c r="E48">
-        <v>-18.63918297838276</v>
+        <v>-20.56992051392306</v>
       </c>
       <c r="F48">
-        <v>-2.758986298401028</v>
+        <v>-2.810628379026355</v>
       </c>
       <c r="G48">
-        <v>-5.351862174909527</v>
+        <v>-4.754682796717016</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.640306155474009</v>
       </c>
       <c r="E49">
-        <v>-19.10087901736079</v>
+        <v>-19.80062334950002</v>
       </c>
       <c r="F49">
-        <v>-2.762501889658509</v>
+        <v>-2.993594857487099</v>
       </c>
       <c r="G49">
-        <v>-5.081781248724706</v>
+        <v>-4.207065595792933</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.868616810076865</v>
       </c>
       <c r="E50">
-        <v>-18.34209696958356</v>
+        <v>-20.19549722602086</v>
       </c>
       <c r="F50">
-        <v>-2.728138724688177</v>
+        <v>-2.904578496382264</v>
       </c>
       <c r="G50">
-        <v>-4.09597692967715</v>
+        <v>-4.33590209654475</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.066352420050517</v>
       </c>
       <c r="E51">
-        <v>-18.55077810880502</v>
+        <v>-19.81685340034351</v>
       </c>
       <c r="F51">
-        <v>-2.947693362963172</v>
+        <v>-3.235547721966389</v>
       </c>
       <c r="G51">
-        <v>-5.05532336877485</v>
+        <v>-4.987255241941895</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.219875612561241</v>
       </c>
       <c r="E52">
-        <v>-17.75587695234261</v>
+        <v>-18.7192011140983</v>
       </c>
       <c r="F52">
-        <v>-3.024241137921069</v>
+        <v>-3.303185577139774</v>
       </c>
       <c r="G52">
-        <v>-4.383305798121574</v>
+        <v>-4.679642660978356</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.322425183361445</v>
       </c>
       <c r="E53">
-        <v>-17.50453758796889</v>
+        <v>-19.400922119687</v>
       </c>
       <c r="F53">
-        <v>-3.027743475300105</v>
+        <v>-3.230799520013542</v>
       </c>
       <c r="G53">
-        <v>-4.525900926134602</v>
+        <v>-4.284092058855156</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.371536818963345</v>
       </c>
       <c r="E54">
-        <v>-16.79751599809934</v>
+        <v>-18.48393783245181</v>
       </c>
       <c r="F54">
-        <v>-3.218808901858019</v>
+        <v>-3.486805637481327</v>
       </c>
       <c r="G54">
-        <v>-5.532167727160394</v>
+        <v>-4.831143156492024</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.371603477767414</v>
       </c>
       <c r="E55">
-        <v>-15.86777047111053</v>
+        <v>-17.08988333698255</v>
       </c>
       <c r="F55">
-        <v>-3.479934329875105</v>
+        <v>-3.367618478831728</v>
       </c>
       <c r="G55">
-        <v>-4.818966969998584</v>
+        <v>-4.525218953753512</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.329924289129669</v>
       </c>
       <c r="E56">
-        <v>-15.90532057758213</v>
+        <v>-17.32977471906488</v>
       </c>
       <c r="F56">
-        <v>-2.933375032405783</v>
+        <v>-3.654537611037185</v>
       </c>
       <c r="G56">
-        <v>-4.748948931842999</v>
+        <v>-4.74235432512877</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.258381615150115</v>
       </c>
       <c r="E57">
-        <v>-15.72597036450835</v>
+        <v>-16.16408663932843</v>
       </c>
       <c r="F57">
-        <v>-3.396410873018234</v>
+        <v>-3.077450489672492</v>
       </c>
       <c r="G57">
-        <v>-4.978935841001707</v>
+        <v>-5.030583661959876</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.170080062616006</v>
       </c>
       <c r="E58">
-        <v>-15.46332340053747</v>
+        <v>-16.32563542107806</v>
       </c>
       <c r="F58">
-        <v>-3.421827670038331</v>
+        <v>-3.426515401170773</v>
       </c>
       <c r="G58">
-        <v>-4.847546909639112</v>
+        <v>-5.393065224691297</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.078933765240934</v>
       </c>
       <c r="E59">
-        <v>-15.409321347996</v>
+        <v>-16.58426110013012</v>
       </c>
       <c r="F59">
-        <v>-3.217437953806386</v>
+        <v>-3.372710453256737</v>
       </c>
       <c r="G59">
-        <v>-4.878368088609727</v>
+        <v>-5.127417118983559</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.998185761156281</v>
       </c>
       <c r="E60">
-        <v>-14.52413147676866</v>
+        <v>-15.69891726078652</v>
       </c>
       <c r="F60">
-        <v>-3.532260641975144</v>
+        <v>-3.765143711761183</v>
       </c>
       <c r="G60">
-        <v>-5.108507282863242</v>
+        <v>-5.149991729015849</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.93848852706176</v>
       </c>
       <c r="E61">
-        <v>-15.08713400777228</v>
+        <v>-15.82357256479566</v>
       </c>
       <c r="F61">
-        <v>-3.464446344544962</v>
+        <v>-3.846643467053015</v>
       </c>
       <c r="G61">
-        <v>-4.921640229353541</v>
+        <v>-5.353649869500734</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.909552385634996</v>
       </c>
       <c r="E62">
-        <v>-13.77237762065134</v>
+        <v>-15.57527180648109</v>
       </c>
       <c r="F62">
-        <v>-3.713535594199371</v>
+        <v>-3.619346907031456</v>
       </c>
       <c r="G62">
-        <v>-5.729069044199626</v>
+        <v>-5.492646434512574</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.916204749542515</v>
       </c>
       <c r="E63">
-        <v>-13.9322916232842</v>
+        <v>-15.29874506967671</v>
       </c>
       <c r="F63">
-        <v>-3.309807546157753</v>
+        <v>-3.634776078275999</v>
       </c>
       <c r="G63">
-        <v>-5.412653722647164</v>
+        <v>-5.430835238748842</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.962579296235569</v>
       </c>
       <c r="E64">
-        <v>-13.93003644322838</v>
+        <v>-15.17005489532673</v>
       </c>
       <c r="F64">
-        <v>-3.884705292476847</v>
+        <v>-3.549415302519719</v>
       </c>
       <c r="G64">
-        <v>-5.77910462948017</v>
+        <v>-5.45546238701548</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.046570351410623</v>
       </c>
       <c r="E65">
-        <v>-13.07842973524192</v>
+        <v>-14.44491940942649</v>
       </c>
       <c r="F65">
-        <v>-3.914539772856074</v>
+        <v>-3.887216074074732</v>
       </c>
       <c r="G65">
-        <v>-6.143350712984022</v>
+        <v>-5.789264693740194</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.165007132110343</v>
       </c>
       <c r="E66">
-        <v>-12.7989277910145</v>
+        <v>-14.12952930868828</v>
       </c>
       <c r="F66">
-        <v>-3.645219306123093</v>
+        <v>-4.003277802513568</v>
       </c>
       <c r="G66">
-        <v>-5.834691999630073</v>
+        <v>-6.196491589980403</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.308376507508692</v>
       </c>
       <c r="E67">
-        <v>-13.07696250966344</v>
+        <v>-14.9935123361377</v>
       </c>
       <c r="F67">
-        <v>-3.825933453615625</v>
+        <v>-3.884091472231372</v>
       </c>
       <c r="G67">
-        <v>-5.748823069432457</v>
+        <v>-6.069651348188767</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.468003641015341</v>
       </c>
       <c r="E68">
-        <v>-13.31636481655294</v>
+        <v>-14.41177097969035</v>
       </c>
       <c r="F68">
-        <v>-4.011495207149339</v>
+        <v>-4.070765723187047</v>
       </c>
       <c r="G68">
-        <v>-6.549091174277099</v>
+        <v>-5.795101185525929</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.631058436937032</v>
       </c>
       <c r="E69">
-        <v>-12.68392266511571</v>
+        <v>-14.46596775661414</v>
       </c>
       <c r="F69">
-        <v>-3.933904517631318</v>
+        <v>-3.710594889919433</v>
       </c>
       <c r="G69">
-        <v>-5.879099657493857</v>
+        <v>-6.134961790587509</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.787782448379728</v>
       </c>
       <c r="E70">
-        <v>-13.78872541181903</v>
+        <v>-14.63171443376889</v>
       </c>
       <c r="F70">
-        <v>-4.023073298338268</v>
+        <v>-4.239918346838706</v>
       </c>
       <c r="G70">
-        <v>-5.461659728264996</v>
+        <v>-6.236062540811312</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.927573660711831</v>
       </c>
       <c r="E71">
-        <v>-13.01793837944746</v>
+        <v>-15.06038431180897</v>
       </c>
       <c r="F71">
-        <v>-3.956801421012099</v>
+        <v>-4.308109551437161</v>
       </c>
       <c r="G71">
-        <v>-6.03125233047876</v>
+        <v>-5.729026007107615</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.045212200441722</v>
       </c>
       <c r="E72">
-        <v>-13.16893581675922</v>
+        <v>-14.21131354926681</v>
       </c>
       <c r="F72">
-        <v>-4.006365127823802</v>
+        <v>-4.058492631747169</v>
       </c>
       <c r="G72">
-        <v>-5.526334545920197</v>
+        <v>-5.477643042128597</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.135644329761787</v>
       </c>
       <c r="E73">
-        <v>-13.99212182187354</v>
+        <v>-14.35756967429254</v>
       </c>
       <c r="F73">
-        <v>-3.977728466709023</v>
+        <v>-4.247438266121319</v>
       </c>
       <c r="G73">
-        <v>-5.991721106194324</v>
+        <v>-5.853840195029218</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.198850693388287</v>
       </c>
       <c r="E74">
-        <v>-13.95093987924779</v>
+        <v>-14.72881397344135</v>
       </c>
       <c r="F74">
-        <v>-4.107177440744501</v>
+        <v>-4.336834019496637</v>
       </c>
       <c r="G74">
-        <v>-5.574446704242426</v>
+        <v>-5.619337701754943</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.235323895327427</v>
       </c>
       <c r="E75">
-        <v>-13.73349161434747</v>
+        <v>-15.12775441962108</v>
       </c>
       <c r="F75">
-        <v>-4.228716334450648</v>
+        <v>-4.712720639130163</v>
       </c>
       <c r="G75">
-        <v>-5.664304841814864</v>
+        <v>-5.373105945635031</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.249395198040426</v>
       </c>
       <c r="E76">
-        <v>-14.30643414579793</v>
+        <v>-14.7692804171739</v>
       </c>
       <c r="F76">
-        <v>-4.385079793770485</v>
+        <v>-4.809604833826787</v>
       </c>
       <c r="G76">
-        <v>-5.466360702930761</v>
+        <v>-5.467055917494008</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.246425365985568</v>
       </c>
       <c r="E77">
-        <v>-14.20705225522559</v>
+        <v>-15.34464115374445</v>
       </c>
       <c r="F77">
-        <v>-4.201259268517456</v>
+        <v>-4.775945781148835</v>
       </c>
       <c r="G77">
-        <v>-4.360105494982362</v>
+        <v>-5.422853513453659</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.233402472456606</v>
       </c>
       <c r="E78">
-        <v>-14.70624405898713</v>
+        <v>-15.48234299136969</v>
       </c>
       <c r="F78">
-        <v>-4.307701994674984</v>
+        <v>-4.647509072079577</v>
       </c>
       <c r="G78">
-        <v>-5.157225271019157</v>
+        <v>-5.130780633251458</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.218387451629942</v>
       </c>
       <c r="E79">
-        <v>-14.80518668758071</v>
+        <v>-16.5296975168117</v>
       </c>
       <c r="F79">
-        <v>-4.687810802960579</v>
+        <v>-4.843289565894226</v>
       </c>
       <c r="G79">
-        <v>-5.173158926699669</v>
+        <v>-5.337262669081341</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.207606761612463</v>
       </c>
       <c r="E80">
-        <v>-15.75751118597177</v>
+        <v>-16.51016620841662</v>
       </c>
       <c r="F80">
-        <v>-4.617570217407597</v>
+        <v>-4.509392061541204</v>
       </c>
       <c r="G80">
-        <v>-4.635830901311641</v>
+        <v>-4.306676600524064</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.207540443822716</v>
       </c>
       <c r="E81">
-        <v>-15.96887318180577</v>
+        <v>-17.41959247253301</v>
       </c>
       <c r="F81">
-        <v>-4.986741262506628</v>
+        <v>-5.205537944608062</v>
       </c>
       <c r="G81">
-        <v>-4.618715380873609</v>
+        <v>-4.516866447357931</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.220109827611982</v>
       </c>
       <c r="E82">
-        <v>-16.59884731490883</v>
+        <v>-18.34638543446882</v>
       </c>
       <c r="F82">
-        <v>-4.75593573816681</v>
+        <v>-5.347312197229794</v>
       </c>
       <c r="G82">
-        <v>-4.579084840222993</v>
+        <v>-4.891259352939649</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.247559502316517</v>
       </c>
       <c r="E83">
-        <v>-17.3666274405393</v>
+        <v>-18.86778940323798</v>
       </c>
       <c r="F83">
-        <v>-5.059551443743094</v>
+        <v>-5.235668980517491</v>
       </c>
       <c r="G83">
-        <v>-4.88067222830506</v>
+        <v>-4.573029852431667</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.287109508207992</v>
       </c>
       <c r="E84">
-        <v>-19.36502037775419</v>
+        <v>-18.93350208956328</v>
       </c>
       <c r="F84">
-        <v>-5.310618834755387</v>
+        <v>-5.471661741533639</v>
       </c>
       <c r="G84">
-        <v>-4.340000551922368</v>
+        <v>-4.28257251845263</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.338748262354982</v>
       </c>
       <c r="E85">
-        <v>-19.4450203995737</v>
+        <v>-19.8414067864131</v>
       </c>
       <c r="F85">
-        <v>-5.124817683042264</v>
+        <v>-5.389153863112599</v>
       </c>
       <c r="G85">
-        <v>-4.641435654909627</v>
+        <v>-5.111374215300251</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.398235673363978</v>
       </c>
       <c r="E86">
-        <v>-21.05384230333073</v>
+        <v>-22.34657672135237</v>
       </c>
       <c r="F86">
-        <v>-5.277499049256657</v>
+        <v>-5.542116874243946</v>
       </c>
       <c r="G86">
-        <v>-4.525086531931941</v>
+        <v>-4.68480380147408</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.464843377659765</v>
       </c>
       <c r="E87">
-        <v>-22.62557600496494</v>
+        <v>-22.99744976200082</v>
       </c>
       <c r="F87">
-        <v>-5.745915964517693</v>
+        <v>-5.740846356012561</v>
       </c>
       <c r="G87">
-        <v>-4.709540197743515</v>
+        <v>-3.99122464772353</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.534321835444931</v>
       </c>
       <c r="E88">
-        <v>-23.33672756312949</v>
+        <v>-24.12786102921752</v>
       </c>
       <c r="F88">
-        <v>-5.357773649159749</v>
+        <v>-6.027114391439417</v>
       </c>
       <c r="G88">
-        <v>-4.995121098143204</v>
+        <v>-4.91968700748537</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.607438968734223</v>
       </c>
       <c r="E89">
-        <v>-25.00798806650429</v>
+        <v>-26.10972050783041</v>
       </c>
       <c r="F89">
-        <v>-5.917963732242137</v>
+        <v>-5.949840966636668</v>
       </c>
       <c r="G89">
-        <v>-4.566448487899596</v>
+        <v>-4.519309629965913</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.681755826582418</v>
       </c>
       <c r="E90">
-        <v>-26.92461940551069</v>
+        <v>-27.70431394625534</v>
       </c>
       <c r="F90">
-        <v>-6.006879860891233</v>
+        <v>-5.868385114817184</v>
       </c>
       <c r="G90">
-        <v>-5.489580869343209</v>
+        <v>-4.857892364449334</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.761448270479276</v>
       </c>
       <c r="E91">
-        <v>-28.66352625361206</v>
+        <v>-30.2550561793708</v>
       </c>
       <c r="F91">
-        <v>-5.801869697474592</v>
+        <v>-6.127835583945808</v>
       </c>
       <c r="G91">
-        <v>-6.023826776834175</v>
+        <v>-5.161048951117015</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.847809557922906</v>
       </c>
       <c r="E92">
-        <v>-30.64101575480754</v>
+        <v>-31.49466027609745</v>
       </c>
       <c r="F92">
-        <v>-6.123645701622449</v>
+        <v>-6.193289862645415</v>
       </c>
       <c r="G92">
-        <v>-6.03689018953214</v>
+        <v>-5.859438327536125</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.950339599623605</v>
       </c>
       <c r="E93">
-        <v>-31.42415872850903</v>
+        <v>-32.75172164012367</v>
       </c>
       <c r="F93">
-        <v>-5.978424612237667</v>
+        <v>-6.30327675873582</v>
       </c>
       <c r="G93">
-        <v>-6.731263874212114</v>
+        <v>-6.279288333917576</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.074134374664764</v>
       </c>
       <c r="E94">
-        <v>-34.46782535735942</v>
+        <v>-34.75201880065878</v>
       </c>
       <c r="F94">
-        <v>-6.066666449820884</v>
+        <v>-6.24414747934029</v>
       </c>
       <c r="G94">
-        <v>-6.805565758295517</v>
+        <v>-6.199769030064282</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.228461781081456</v>
       </c>
       <c r="E95">
-        <v>-35.89078510241963</v>
+        <v>-36.56336764746086</v>
       </c>
       <c r="F95">
-        <v>-5.86099524921681</v>
+        <v>-6.218602285372759</v>
       </c>
       <c r="G95">
-        <v>-7.591032414034077</v>
+        <v>-7.255068321072219</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.42384359059611</v>
       </c>
       <c r="E96">
-        <v>-38.61643737984436</v>
+        <v>-39.02528839138987</v>
       </c>
       <c r="F96">
-        <v>-5.968175222362829</v>
+        <v>-5.89009413934235</v>
       </c>
       <c r="G96">
-        <v>-7.86774105238852</v>
+        <v>-6.882396899170922</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.660718148515021</v>
       </c>
       <c r="E97">
-        <v>-41.93788060432524</v>
+        <v>-41.34952994006369</v>
       </c>
       <c r="F97">
-        <v>-6.188602959880375</v>
+        <v>-5.952012945966808</v>
       </c>
       <c r="G97">
-        <v>-8.141811185948164</v>
+        <v>-7.967176598206069</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.957745185589665</v>
       </c>
       <c r="E98">
-        <v>-43.46680211269094</v>
+        <v>-43.81785847471356</v>
       </c>
       <c r="F98">
-        <v>-5.69384561794512</v>
+        <v>-6.216697868713723</v>
       </c>
       <c r="G98">
-        <v>-8.746849799250905</v>
+        <v>-7.736295841751757</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.296728707144623</v>
       </c>
       <c r="E99">
-        <v>-45.97604314576311</v>
+        <v>-46.02817946701342</v>
       </c>
       <c r="F99">
-        <v>-5.803851152302088</v>
+        <v>-6.184833888197637</v>
       </c>
       <c r="G99">
-        <v>-9.576015656107845</v>
+        <v>-8.670846294760317</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.712810394763211</v>
       </c>
       <c r="E100">
-        <v>-48.90003352777578</v>
+        <v>-49.17056682923101</v>
       </c>
       <c r="F100">
-        <v>-5.751842933284724</v>
+        <v>-6.287280984187761</v>
       </c>
       <c r="G100">
-        <v>-10.03885640686227</v>
+        <v>-8.499330240916215</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.148387056492685</v>
       </c>
       <c r="E101">
-        <v>-50.43132569228449</v>
+        <v>-51.04752533957471</v>
       </c>
       <c r="F101">
-        <v>-5.897392884528417</v>
+        <v>-6.096155500993144</v>
       </c>
       <c r="G101">
-        <v>-10.27916890755797</v>
+        <v>-9.462649334661043</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.691020019384921</v>
       </c>
       <c r="E102">
-        <v>-52.7649502391022</v>
+        <v>-53.08085885011429</v>
       </c>
       <c r="F102">
-        <v>-5.592655569488743</v>
+        <v>-6.360196782268084</v>
       </c>
       <c r="G102">
-        <v>-10.42807393536884</v>
+        <v>-10.07710645002301</v>
       </c>
     </row>
   </sheetData>
